--- a/banking_application_forms/015_mortgage_pre_approval_verification_form--banking_application_forms.xlsx
+++ b/banking_application_forms/015_mortgage_pre_approval_verification_form--banking_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -807,8 +807,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -836,12 +836,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'700-799'}</t>
+          <t>700-799</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '700-799'}</t>
+          <t>700-799</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'800-849'}</t>
+          <t>800-849</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '800-849'}</t>
+          <t>800-849</t>
         </is>
       </c>
     </row>
@@ -870,12 +870,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'850-899'}</t>
+          <t>850-899</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '850-899'}</t>
+          <t>850-899</t>
         </is>
       </c>
     </row>
@@ -887,12 +887,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'900-949'}</t>
+          <t>900-949</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': '900-949'}</t>
+          <t>900-949</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'950-999'}</t>
+          <t>950-999</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': '950-999'}</t>
+          <t>950-999</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'1000_or_higher'}</t>
+          <t>1000_or_higher</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': '1000 or higher'}</t>
+          <t>1000 or higher</t>
         </is>
       </c>
     </row>
@@ -938,12 +938,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'less_than_5_years'}</t>
+          <t>less_than_5_years</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Less than 5 years'}</t>
+          <t>Less than 5 years</t>
         </is>
       </c>
     </row>
@@ -955,12 +955,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'5-10_years'}</t>
+          <t>5-10_years</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '5-10 years'}</t>
+          <t>5-10 years</t>
         </is>
       </c>
     </row>
@@ -972,12 +972,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'10-15_years'}</t>
+          <t>10-15_years</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '10-15 years'}</t>
+          <t>10-15 years</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'15-20_years'}</t>
+          <t>15-20_years</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': '15-20 years'}</t>
+          <t>15-20 years</t>
         </is>
       </c>
     </row>
@@ -1006,12 +1006,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'20_or_more_years'}</t>
+          <t>20_or_more_years</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': '20 or more years'}</t>
+          <t>20 or more years</t>
         </is>
       </c>
     </row>
@@ -1023,12 +1023,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'co_applicant_1'}</t>
+          <t>co_applicant_1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Co Applicant 1'}</t>
+          <t>Co Applicant 1</t>
         </is>
       </c>
     </row>
@@ -1040,12 +1040,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'co_applicant_2'}</t>
+          <t>co_applicant_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Co Applicant 2'}</t>
+          <t>Co Applicant 2</t>
         </is>
       </c>
     </row>
@@ -1057,12 +1057,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'no_co_applicant'}</t>
+          <t>no_co_applicant</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'No Co Applicant'}</t>
+          <t>No Co Applicant</t>
         </is>
       </c>
     </row>
